--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N143_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N143_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.99760515224365</v>
+        <v>4.712110837239593</v>
       </c>
       <c r="D2" t="n">
-        <v>29.54388353674828</v>
+        <v>4.800881074721596</v>
       </c>
       <c r="E2" t="n">
-        <v>5.331208092291045</v>
+        <v>0.8663213149972948</v>
       </c>
       <c r="F2" t="n">
-        <v>5.173044634350441</v>
+        <v>0.8406197530819467</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>42.47682468675022</v>
+        <v>6.902484011596911</v>
       </c>
       <c r="D3" t="n">
-        <v>42.79770498622254</v>
+        <v>6.954627060261164</v>
       </c>
       <c r="E3" t="n">
-        <v>5.331208092291045</v>
+        <v>0.8663213149972948</v>
       </c>
       <c r="F3" t="n">
-        <v>5.173044634350441</v>
+        <v>0.8406197530819467</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.41781003633221</v>
+        <v>4.455394130903985</v>
       </c>
       <c r="D4" t="n">
-        <v>27.87290649250682</v>
+        <v>4.529347305032358</v>
       </c>
       <c r="E4" t="n">
-        <v>5.331208092291045</v>
+        <v>0.8663213149972948</v>
       </c>
       <c r="F4" t="n">
-        <v>5.173044634350441</v>
+        <v>0.8406197530819467</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.45921008932043</v>
+        <v>5.27462163951457</v>
       </c>
       <c r="D5" t="n">
-        <v>32.58966358203149</v>
+        <v>5.295820332080117</v>
       </c>
       <c r="E5" t="n">
-        <v>5.331208092291045</v>
+        <v>0.8663213149972948</v>
       </c>
       <c r="F5" t="n">
-        <v>5.173044634350441</v>
+        <v>0.8406197530819467</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.21570019793734</v>
+        <v>6.210051282164819</v>
       </c>
       <c r="D6" t="n">
-        <v>38.05044515013198</v>
+        <v>6.183197336896447</v>
       </c>
       <c r="E6" t="n">
-        <v>5.331208092291045</v>
+        <v>0.8663213149972948</v>
       </c>
       <c r="F6" t="n">
-        <v>5.173044634350441</v>
+        <v>0.8406197530819467</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.41478737981514</v>
+        <v>6.07990294921996</v>
       </c>
       <c r="D7" t="n">
-        <v>37.17399871308736</v>
+        <v>6.040774790876696</v>
       </c>
       <c r="E7" t="n">
-        <v>5.331208092291045</v>
+        <v>0.8663213149972948</v>
       </c>
       <c r="F7" t="n">
-        <v>5.173044634350441</v>
+        <v>0.8406197530819467</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
